--- a/MA.xlsx
+++ b/MA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD87083E-0CB2-4490-ACA1-9C3D954D3484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4571DFE2-964E-402B-8FC7-D5F05EC94387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52440" yWindow="2670" windowWidth="24340" windowHeight="16340" xr2:uid="{E7BFF71A-2904-4F34-A901-1B8DEA033DF8}"/>
+    <workbookView xWindow="21420" yWindow="4210" windowWidth="20170" windowHeight="14480" activeTab="1" xr2:uid="{E7BFF71A-2904-4F34-A901-1B8DEA033DF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>Price</t>
   </si>
@@ -142,6 +142,39 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Payment Network</t>
+  </si>
+  <si>
+    <t>VAS</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Other Network</t>
+  </si>
+  <si>
+    <t>Transaction Processing</t>
+  </si>
+  <si>
+    <t>Domestic assessments</t>
+  </si>
+  <si>
+    <t>Cross-border assessments</t>
   </si>
 </sst>
 </file>
@@ -231,6 +264,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33131</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>27609</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33131</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{011E295D-8D17-FF9F-2843-94DD90136A53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8045174" y="27609"/>
+          <a:ext cx="0" cy="7360478"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,20 +708,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{205891AB-6F07-4B83-AF2A-CD982404D2A5}">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="8.7265625" style="5"/>
+    <col min="3" max="14" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
@@ -658,17 +746,29 @@
       <c r="J2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L2">
+      <c r="K2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2">
         <v>2022</v>
       </c>
-      <c r="M2">
+      <c r="Q2">
         <v>2023</v>
       </c>
-      <c r="N2">
+      <c r="R2">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -680,11 +780,15 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="N3" s="3">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="R3" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -696,11 +800,15 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="N4" s="3">
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="R4" s="3">
         <v>3634</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -712,11 +820,15 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
-      <c r="N5" s="3">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="R5" s="3">
         <v>4865</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -728,11 +840,15 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
-      <c r="N6" s="3">
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="R6" s="3">
         <v>1258</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -744,11 +860,15 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="N7" s="3">
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="R7" s="3">
         <v>159.4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -757,8 +877,12 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
@@ -770,12 +894,16 @@
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="N9" s="3">
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="R9" s="3">
         <f>1070+1035+153</f>
         <v>2258</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -784,415 +912,782 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:14" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2470</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2596</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2641</v>
+      </c>
+      <c r="F11" s="7">
+        <f>10245-E11-D11-C11</f>
+        <v>2538</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2658</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2789</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2809</v>
+      </c>
+      <c r="J11" s="7">
+        <f>11029-I11-H11-G11</f>
+        <v>2773</v>
+      </c>
+      <c r="K11" s="7">
+        <v>2896</v>
+      </c>
+      <c r="L11" s="7">
+        <v>3154</v>
+      </c>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2338</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2433</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2804</v>
+      </c>
+      <c r="F12" s="7">
+        <f>10181-E12-D12-C12</f>
+        <v>2606</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2595</v>
+      </c>
+      <c r="H12" s="7">
+        <v>2848</v>
+      </c>
+      <c r="I12" s="7">
+        <v>3313</v>
+      </c>
+      <c r="J12" s="7">
+        <f>12021-I12-H12-G12</f>
+        <v>3265</v>
+      </c>
+      <c r="K12" s="7">
+        <v>3190</v>
+      </c>
+      <c r="L12" s="7">
+        <v>3460</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3086</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3324</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3587</v>
+      </c>
+      <c r="F13" s="7">
+        <f>13602-E13-D13-C13</f>
+        <v>3605</v>
+      </c>
+      <c r="G13" s="7">
+        <v>3527</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2971</v>
+      </c>
+      <c r="I13" s="7">
+        <v>4191</v>
+      </c>
+      <c r="J13" s="7">
+        <f>15930-I13-H13-G13</f>
+        <v>5241</v>
+      </c>
+      <c r="K13" s="7">
+        <v>4224</v>
+      </c>
+      <c r="L13" s="7">
+        <v>4508</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7">
+        <v>226</v>
+      </c>
+      <c r="D14" s="7">
+        <v>244</v>
+      </c>
+      <c r="E14" s="7">
+        <v>227</v>
+      </c>
+      <c r="F14" s="7">
+        <f>936-E14-D14-C14</f>
+        <v>239</v>
+      </c>
+      <c r="G14" s="7">
+        <v>231</v>
+      </c>
+      <c r="H14" s="7">
+        <v>260</v>
+      </c>
+      <c r="I14" s="7">
+        <v>255</v>
+      </c>
+      <c r="J14" s="7">
+        <f>1018-I14-H14-G14</f>
+        <v>272</v>
+      </c>
+      <c r="K14" s="7">
+        <v>277</v>
+      </c>
+      <c r="L14" s="7">
+        <v>326</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" ref="C15:F15" si="0">SUM(C11:C14)</f>
+        <v>8120</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>8597</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="0"/>
+        <v>9259</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>8988</v>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G11:G14)</f>
+        <v>9011</v>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(H11:H14)</f>
+        <v>8868</v>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(I11:I14)</f>
+        <v>10568</v>
+      </c>
+      <c r="J15" s="7">
+        <f>SUM(J11:J14)</f>
+        <v>11551</v>
+      </c>
+      <c r="K15" s="7">
+        <f>SUM(K11:K14)</f>
+        <v>10587</v>
+      </c>
+      <c r="L15" s="7">
+        <f>SUM(L11:L14)</f>
+        <v>11448</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3920</v>
+      </c>
+      <c r="D16" s="7">
+        <v>4375</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4629</v>
+      </c>
+      <c r="F16" s="7">
+        <f>17335-E16-D16-C16</f>
+        <v>4411</v>
+      </c>
+      <c r="G16" s="7">
+        <v>4432</v>
+      </c>
+      <c r="H16" s="7">
+        <v>4945</v>
+      </c>
+      <c r="I16" s="7">
+        <v>5179</v>
+      </c>
+      <c r="J16" s="7">
+        <f>19476-I16-H16-G16</f>
+        <v>4920</v>
+      </c>
+      <c r="K16" s="7">
+        <v>4948</v>
+      </c>
+      <c r="L16" s="7">
+        <v>5451</v>
+      </c>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2428</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2586</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2740</v>
+      </c>
+      <c r="F17" s="7">
+        <f>10832-E17-D17-C17</f>
+        <v>3078</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2818</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3188</v>
+      </c>
+      <c r="I17" s="7">
+        <v>3423</v>
+      </c>
+      <c r="J17" s="7">
+        <f>13315-I17-H17-G17</f>
+        <v>3886</v>
+      </c>
+      <c r="K17" s="7">
+        <v>3450</v>
+      </c>
+      <c r="L17" s="7">
+        <v>3826</v>
+      </c>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+    </row>
+    <row r="18" spans="2:18" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8">
+      <c r="C18" s="8">
+        <f>+C17+C16</f>
+        <v>6348</v>
+      </c>
+      <c r="D18" s="8">
+        <f>+D17+D16</f>
         <v>6961</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8">
+      <c r="E18" s="8">
+        <f>+E17+E16</f>
+        <v>7369</v>
+      </c>
+      <c r="F18" s="8">
+        <f>+F17+F16</f>
+        <v>7489</v>
+      </c>
+      <c r="G18" s="8">
+        <f>+G17+G16</f>
+        <v>7250</v>
+      </c>
+      <c r="H18" s="8">
+        <f>+H17+H16</f>
         <v>8133</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="L11" s="4">
+      <c r="I18" s="8">
+        <f>+I17+I16</f>
+        <v>8602</v>
+      </c>
+      <c r="J18" s="8">
+        <f>+J17+J16</f>
+        <v>8806</v>
+      </c>
+      <c r="K18" s="8">
+        <f>+K17+K16</f>
+        <v>8398</v>
+      </c>
+      <c r="L18" s="8">
+        <f>+L17+L16</f>
+        <v>9277</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="P18" s="4">
         <v>22237</v>
       </c>
-      <c r="M11" s="4">
+      <c r="Q18" s="4">
         <v>25098</v>
       </c>
-      <c r="N11" s="4">
+      <c r="R18" s="4">
         <v>28167</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="19" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7">
         <v>2418</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7">
         <v>2766</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="L12" s="3">
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="P19" s="3">
         <v>8078</v>
       </c>
-      <c r="M12" s="3">
+      <c r="Q19" s="3">
         <v>8927</v>
       </c>
-      <c r="N12" s="3">
+      <c r="R19" s="3">
         <v>10193</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+    <row r="20" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7">
-        <v>184</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7">
-        <v>213</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="L13" s="3">
-        <v>789</v>
-      </c>
-      <c r="M13" s="3">
-        <v>825</v>
-      </c>
-      <c r="N13" s="3">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7">
-        <f>+D11-D12-D13</f>
-        <v>4359</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7">
-        <f>+H11-H12-H13</f>
-        <v>5154</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="L14" s="3">
-        <f>+L11-L12-L13</f>
-        <v>13370</v>
-      </c>
-      <c r="M14" s="3">
-        <f>+M11-M12-M13</f>
-        <v>15346</v>
-      </c>
-      <c r="N14" s="3">
-        <f>+N11-N12-N13</f>
-        <v>17159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7">
-        <f>60-153+9</f>
-        <v>-84</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7">
-        <f>70-195+16</f>
-        <v>-109</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="L15" s="3">
-        <f>61-471</f>
-        <v>-410</v>
-      </c>
-      <c r="M15" s="3">
-        <f>274-575</f>
-        <v>-301</v>
-      </c>
-      <c r="N15" s="3">
-        <f>327-646</f>
-        <v>-319</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7">
-        <f>+D14+D15</f>
-        <v>4275</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7">
-        <f>+H14+H15</f>
-        <v>5045</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="L16" s="3">
-        <f t="shared" ref="L16:M16" si="0">+L14+L15</f>
-        <v>12960</v>
-      </c>
-      <c r="M16" s="3">
-        <f t="shared" si="0"/>
-        <v>15045</v>
-      </c>
-      <c r="N16" s="3">
-        <f>+N14+N15</f>
-        <v>16840</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7">
-        <v>681</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7">
-        <v>971</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="L17" s="3">
-        <v>1802</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2444</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7">
-        <f>+D16-D17</f>
-        <v>3594</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7">
-        <f>+H16-H17</f>
-        <v>4074</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="L18" s="3">
-        <f>+L16-L17</f>
-        <v>11158</v>
-      </c>
-      <c r="M18" s="3">
-        <f>+M16-M17</f>
-        <v>12601</v>
-      </c>
-      <c r="N18" s="3">
-        <f>+N16-N17</f>
-        <v>14460</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9">
-        <f>+D18/D20</f>
-        <v>3.8645161290322583</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9">
-        <f>+H18/H20</f>
-        <v>4.4818481848184817</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1">
-        <f t="shared" ref="L19:M19" si="1">+L18/L20</f>
-        <v>11.49124613800206</v>
-      </c>
-      <c r="M19" s="1">
-        <f t="shared" si="1"/>
-        <v>13.32029598308668</v>
-      </c>
-      <c r="N19" s="1">
-        <f>+N18/N20</f>
-        <v>15.598705501618124</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7">
-        <v>930</v>
+        <v>184</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7">
-        <v>909</v>
+        <v>213</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3">
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="P20" s="3">
+        <v>789</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>825</v>
+      </c>
+      <c r="R20" s="3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7">
+        <f>+D18-D19-D20</f>
+        <v>4359</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7">
+        <f>+H18-H19-H20</f>
+        <v>5154</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="P21" s="3">
+        <f>+P18-P19-P20</f>
+        <v>13370</v>
+      </c>
+      <c r="Q21" s="3">
+        <f>+Q18-Q19-Q20</f>
+        <v>15346</v>
+      </c>
+      <c r="R21" s="3">
+        <f>+R18-R19-R20</f>
+        <v>17159</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7">
+        <f>60-153+9</f>
+        <v>-84</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7">
+        <f>70-195+16</f>
+        <v>-109</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="P22" s="3">
+        <f>61-471</f>
+        <v>-410</v>
+      </c>
+      <c r="Q22" s="3">
+        <f>274-575</f>
+        <v>-301</v>
+      </c>
+      <c r="R22" s="3">
+        <f>327-646</f>
+        <v>-319</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7">
+        <f>+D21+D22</f>
+        <v>4275</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7">
+        <f>+H21+H22</f>
+        <v>5045</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="P23" s="3">
+        <f t="shared" ref="P23:Q23" si="1">+P21+P22</f>
+        <v>12960</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="1"/>
+        <v>15045</v>
+      </c>
+      <c r="R23" s="3">
+        <f>+R21+R22</f>
+        <v>16840</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7">
+        <v>681</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7">
         <v>971</v>
       </c>
-      <c r="M20" s="3">
-        <v>946</v>
-      </c>
-      <c r="N20" s="3">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="10">
-        <f>+H11/D11-1</f>
-        <v>0.1683666139922424</v>
-      </c>
-      <c r="M22" s="2">
-        <f>+M11/L11-1</f>
-        <v>0.1286594414714215</v>
-      </c>
-      <c r="N22" s="2">
-        <f>+N11/M11-1</f>
-        <v>0.12228065981353087</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10">
-        <f>+D16/D11</f>
-        <v>0.6141359000143658</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10">
-        <f>+H16/H11</f>
-        <v>0.62031230788147051</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2">
-        <f>+L14/L11</f>
-        <v>0.60125016863785585</v>
-      </c>
-      <c r="M23" s="2">
-        <f>+M14/M11</f>
-        <v>0.61144314287991075</v>
-      </c>
-      <c r="N23" s="2">
-        <f>+N14/N11</f>
-        <v>0.6091880569460717</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3">
-        <v>11195</v>
-      </c>
-      <c r="M26" s="3">
-        <v>11980</v>
-      </c>
-      <c r="N26" s="3">
-        <v>14780</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>26</v>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="P24" s="3">
+        <v>1802</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>2444</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7">
+        <f>+D23-D24</f>
+        <v>3594</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7">
+        <f>+H23-H24</f>
+        <v>4074</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="P25" s="3">
+        <f>+P23-P24</f>
+        <v>11158</v>
+      </c>
+      <c r="Q25" s="3">
+        <f>+Q23-Q24</f>
+        <v>12601</v>
+      </c>
+      <c r="R25" s="3">
+        <f>+R23-R24</f>
+        <v>14460</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9">
+        <f>+D25/D27</f>
+        <v>3.8645161290322583</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9">
+        <f>+H25/H27</f>
+        <v>4.4818481848184817</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1">
+        <f t="shared" ref="P26:Q26" si="2">+P25/P27</f>
+        <v>11.49124613800206</v>
+      </c>
+      <c r="Q26" s="1">
+        <f t="shared" si="2"/>
+        <v>13.32029598308668</v>
+      </c>
+      <c r="R26" s="1">
+        <f>+R25/R27</f>
+        <v>15.598705501618124</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="7">
+        <v>930</v>
+      </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="H27" s="7">
+        <v>909</v>
+      </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3">
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3">
+        <v>971</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>946</v>
+      </c>
+      <c r="R27" s="3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="10">
+        <f>+H18/D18-1</f>
+        <v>0.1683666139922424</v>
+      </c>
+      <c r="Q29" s="2">
+        <f>+Q18/P18-1</f>
+        <v>0.1286594414714215</v>
+      </c>
+      <c r="R29" s="2">
+        <f>+R18/Q18-1</f>
+        <v>0.12228065981353087</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10">
+        <f>+D23/D18</f>
+        <v>0.6141359000143658</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10">
+        <f>+H23/H18</f>
+        <v>0.62031230788147051</v>
+      </c>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2">
+        <f>+P21/P18</f>
+        <v>0.60125016863785585</v>
+      </c>
+      <c r="Q30" s="2">
+        <f>+Q21/Q18</f>
+        <v>0.61144314287991075</v>
+      </c>
+      <c r="R30" s="2">
+        <f>+R21/R18</f>
+        <v>0.6091880569460717</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3">
+        <v>11195</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>11980</v>
+      </c>
+      <c r="R33" s="3">
+        <v>14780</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3">
         <f>-442-655</f>
         <v>-1097</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q34" s="3">
         <f>-371-717</f>
         <v>-1088</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R34" s="3">
         <f>-474-720</f>
         <v>-1194</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3">
-        <f>+L26+L27</f>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3">
+        <f>+P33+P34</f>
         <v>10098</v>
       </c>
-      <c r="M28" s="3">
-        <f>+M26+M27</f>
+      <c r="Q35" s="3">
+        <f>+Q33+Q34</f>
         <v>10892</v>
       </c>
-      <c r="N28" s="3">
-        <f>+N26+N27</f>
+      <c r="R35" s="3">
+        <f>+R33+R34</f>
         <v>13586</v>
       </c>
     </row>
@@ -1201,5 +1696,6 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{692A3948-F9D8-491D-99DB-9365EE33A2B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>